--- a/MMAT_Assessment_AP25796141.xlsx
+++ b/MMAT_Assessment_AP25796141.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +54,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +95,33 @@
         <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7777"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +143,17 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -145,6 +179,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -538,7 +590,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Synthesis corpus: n=73 papers (Tier 1: 42 | Tier 2: 29 | Tier 3: 2 closed-access). Tier R: 2 background references excluded from synthesis. Mean MMAT score: 3.95. Sensitivity analysis: Tier 1+2 only (n=71, 97.3%) yields identical conclusions.</t>
+          <t>Synthesis corpus: n=82 papers (Tier 1: 43 | Tier 2: 37 | Tier 3: 2 closed-access). Tier R: 2 background references excluded from synthesis. Mean MMAT score: 3.88. Sensitivity analysis: Tier 1+2 only (n=80, 97.6%) yields identical conclusions. [Updated after supplementary RQ5 search: +9 papers from IEEE Xplore, Google Scholar, ERIC, CyberLeninka]</t>
         </is>
       </c>
     </row>
@@ -4611,110 +4663,659 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>P076</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Kassenkhan</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>RQ1/RQ2/RQ5</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Systematic/Narrative Review</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="J77" s="13" t="inlineStr">
+        <is>
+          <t>Include (MMAT≥4, full text)</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>Bibliometric analysis (VOSviewer) of 101 gamification+AI+CT publications; co-occurrence mapping</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2025.3576147</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>P077</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>Niyazova</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>Int. J. Innovative Research and Scientific Studies</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>RQ1/RQ5</t>
+        </is>
+      </c>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>Development/Design Study</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J78" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>Ontological models + NLP thesauri for AI-automated smart textbook in Kazakh language</t>
+        </is>
+      </c>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>10.53894/ijirss.v8i3.7020</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>P078</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Ospan</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>IEEE SIST 2025</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>RQ1/RQ5</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Quant. Descriptive</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J79" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>ML-based adaptive platform for Kazakhstan UNT; survey (n=109)</t>
+        </is>
+      </c>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/SIST65741.2025.10977657</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>P079</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>Baumuratova</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>IEEE UBMK 2025</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>RQ1/RQ5</t>
+        </is>
+      </c>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>Mixed Methods (SLR+Survey)</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>AI-adaptive platform for inclusive education; PRISMA 2020 systematic review + survey design</t>
+        </is>
+      </c>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/UBMK65834.2025.10977896</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>P080</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Adhana</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>IEEE ICCAKM 2023</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>RQ3/RQ5</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Quant. Experimental</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J81" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>SVM for adaptive science assessment personalisation (Kazakhstan students)</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/ICCAKM58659.2023.10449617</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>P081</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>Tastanova</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>IEEE ICCAKM 2023</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>RQ4/RQ5</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>Quant. Descriptive</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J82" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>Collaborative filtering + AI for predictive analytics; problem-solving skill development (KZ high school)</t>
+        </is>
+      </c>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/ICCAKM58659.2023.10449421</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>P082</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Merembayev</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>IEEE SIST 2021</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>RQ4/RQ5</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Quant. Experimental</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J83" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>IRT + ML hybrid algorithms for student ability measurement (Kazakhstan)</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/SIST52873.2021.9581480</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>P083</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>Ashimbekova</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>IEEE ITMS 2025</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr">
+        <is>
+          <t>RQ1/RQ5</t>
+        </is>
+      </c>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>Mixed Methods</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J84" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
+          <t>Empirical evaluation of AI (adaptive modules, recommendations, chatbots) in Kazakhstan HE</t>
+        </is>
+      </c>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/ITMS59786.2025.10967219</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>P084</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Yunusaliyev</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>IEEE ICACITE 2024</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>RQ1/RQ5</t>
+        </is>
+      </c>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Mixed Methods</t>
+        </is>
+      </c>
+      <c r="H85" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="J85" s="15" t="inlineStr">
+        <is>
+          <t>Snowball-RQ5</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>Included (Tier 1+2)</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>Hybrid AI techniques for personalized adaptive learning in Uzbekistani HE; review + implementation</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>10.1109/ICACITE60783.2024.10616462</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>P074</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr"/>
-      <c r="D77" s="7" t="n">
+      <c r="C86" s="7" t="inlineStr"/>
+      <c r="D86" s="7" t="n">
         <v>2025</v>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>Smart Learning Environments (Springer Q1)</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>RQ5</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>Systematic/Narrative Review</t>
         </is>
       </c>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Tier R</t>
         </is>
       </c>
-      <c r="J77" s="7" t="inlineStr">
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>Related-Work-Review</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="K86" s="7" t="inlineStr">
         <is>
           <t>N/A (background ref)</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>SLR/Review (PRISMA+AMSTAR2, 933→38 papers)</t>
         </is>
       </c>
-      <c r="M77" s="7" t="inlineStr">
+      <c r="M86" s="7" t="inlineStr">
         <is>
           <t>10.1186/s40561-024-00360-3</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>P075</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="7" t="n">
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="n">
         <v>2022</v>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>Electronic Journal of e-Learning Q2</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>RQ4</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>Quant. Descriptive</t>
-        </is>
-      </c>
-      <c r="H78" s="7" t="n"/>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Quant. Descriptive</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>Tier R</t>
         </is>
       </c>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="J87" s="7" t="inlineStr">
         <is>
           <t>Background-Reference</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K87" s="7" t="inlineStr">
         <is>
           <t>N/A (background ref)</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>Conceptual review (chatbots, expert systems, ML, personalized systems)</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M87" s="7" t="inlineStr">
         <is>
           <t>10.34190/ejel.20.5.2597</t>
         </is>
